--- a/Project3_CRM_System/CRM_Tracking1.xlsx
+++ b/Project3_CRM_System/CRM_Tracking1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\INTERNSHIP -1\ACCOUNTING\CLINCH BRIDGE\FINAL SUBMISSION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamza\OneDrive\Desktop\INTERNSHIP_PROJECT\Project3_CRM_System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12F5F7C-C96A-415C-9DF3-32D83D21B597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8398B181-48FC-4C6C-8D96-61C3D299551A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{670BEDC1-B6B3-460B-9972-6378B8A711E5}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="59">
   <si>
     <t>Lead Name</t>
   </si>
@@ -211,30 +211,6 @@
   </si>
   <si>
     <t>Success</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                      13-04-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                     14-04-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                     15-04-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                      16-04-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                      17-04-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                      18-04-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                      19-04-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                      20-04-2026</t>
   </si>
 </sst>
 </file>
@@ -277,7 +253,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill>
@@ -309,6 +285,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -363,84 +346,7 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -461,7 +367,7 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CF7CE869-9147-49E6-A23C-A57243B76E37}" name="Lead Name"/>
     <tableColumn id="2" xr3:uid="{98C79124-0FC1-451D-A6B8-BBAED4B231F5}" name="Company"/>
-    <tableColumn id="3" xr3:uid="{10948C97-5AE5-412C-AB64-C764A581DF09}" name="Next Follow-up Date" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{10948C97-5AE5-412C-AB64-C764A581DF09}" name="Next Follow-up Date" dataDxfId="13"/>
     <tableColumn id="4" xr3:uid="{32661020-23F8-4F84-BC17-B25C705805FA}" name="Status"/>
     <tableColumn id="5" xr3:uid="{E20CDC26-53E2-4972-A9FD-BE0672476E2D}" name="Priority"/>
     <tableColumn id="6" xr3:uid="{0CA4BA76-0AEB-45EC-99E4-EEC51E52512B}" name="Notes"/>
@@ -767,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A37F7F-70A1-40FB-BBD1-BF59CCF55104}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -1044,8 +950,8 @@
       <c r="B14" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>59</v>
+      <c r="C14" s="1">
+        <v>46125</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
@@ -1064,8 +970,8 @@
       <c r="B15" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>60</v>
+      <c r="C15" s="1">
+        <v>46126</v>
       </c>
       <c r="D15" t="s">
         <v>8</v>
@@ -1084,8 +990,8 @@
       <c r="B16" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>61</v>
+      <c r="C16" s="1">
+        <v>46127</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
@@ -1104,8 +1010,8 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>62</v>
+      <c r="C17" s="1">
+        <v>46128</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
@@ -1124,8 +1030,8 @@
       <c r="B18" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>63</v>
+      <c r="C18" s="1">
+        <v>46129</v>
       </c>
       <c r="D18" t="s">
         <v>8</v>
@@ -1144,8 +1050,8 @@
       <c r="B19" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>64</v>
+      <c r="C19" s="1">
+        <v>46130</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
@@ -1164,8 +1070,8 @@
       <c r="B20" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>65</v>
+      <c r="C20" s="1">
+        <v>46131</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -1184,8 +1090,8 @@
       <c r="B21" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>66</v>
+      <c r="C21" s="1">
+        <v>46132</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
@@ -1197,48 +1103,128 @@
         <v>58</v>
       </c>
     </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C27"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C29"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C30"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C31"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C32"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C33"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C34"/>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C35"/>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C36"/>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C37"/>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C38"/>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C39"/>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C40"/>
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C41"/>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C42"/>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C43"/>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C44"/>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C45"/>
+    </row>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C46"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="containsText" dxfId="19" priority="8" operator="containsText" text="Not Responding">
-      <formula>NOT(ISERROR(SEARCH("Not Responding",D1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="9" operator="containsText" text="Closed">
-      <formula>NOT(ISERROR(SEARCH("Closed",D1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="10" operator="containsText" text="Interested">
-      <formula>NOT(ISERROR(SEARCH("Interested",D1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="11" operator="containsText" text="Follow-up">
-      <formula>NOT(ISERROR(SEARCH("Follow-up",D1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
-    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="Low">
-      <formula>NOT(ISERROR(SEARCH("Low",E2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="6" operator="containsText" text="Medium">
-      <formula>NOT(ISERROR(SEARCH("Medium",E2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="High">
-      <formula>NOT(ISERROR(SEARCH("High",E2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="lessThan">
-      <formula>TODAY()</formula>
+  <conditionalFormatting sqref="C1:C20">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="lessThan">
+      <formula>AND(C2&lt;TODAY(),C2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="11" priority="2" operator="lessThan">
       <formula>TODAY()</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
-      <formula>AND(C2&lt;TODAY(),C2&lt;&gt;"")</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D21 C22:C46">
+    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="Not Responding">
+      <formula>NOT(ISERROR(SEARCH("Not Responding",C1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="Closed">
+      <formula>NOT(ISERROR(SEARCH("Closed",C1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="Interested">
+      <formula>NOT(ISERROR(SEARCH("Interested",C1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="11" operator="containsText" text="Follow-up">
+      <formula>NOT(ISERROR(SEARCH("Follow-up",C1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E21">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="Medium">
+      <formula>NOT(ISERROR(SEARCH("Medium",E2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",E2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21">
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="lessThan">
+      <formula>AND(#REF!&lt;TODAY(),#REF!&lt;&gt;"")</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="lessThan">
+      <formula>TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D21 D22:D1048576" xr:uid="{894FB7D7-67D4-4E5A-9A94-869ABA92F7EF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D21 C22:C46" xr:uid="{894FB7D7-67D4-4E5A-9A94-869ABA92F7EF}">
       <formula1>"Follow-up,Interested,Closed,Not Responding"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E21 E22:E1048576" xr:uid="{A9340BFB-BD32-4F3A-BD09-4468B003A68C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E21 D22:D46" xr:uid="{A9340BFB-BD32-4F3A-BD09-4468B003A68C}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
